--- a/sheets/국악이꽃피는나무/검수/울고넘는 박달재.xlsx
+++ b/sheets/국악이꽃피는나무/검수/울고넘는 박달재.xlsx
@@ -4559,28 +4559,28 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="57.97" customHeight="true">
+    <row r="2" ht="64.52" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="64.69" customHeight="true">
+    <row r="3" ht="72.04" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="Q3" s="22"/>
     </row>
-    <row r="4" ht="64.69" customHeight="true">
+    <row r="4" ht="72.04" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="64.69" customHeight="true">
+    <row r="5" ht="72.04" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="64.69" customHeight="true">
+    <row r="6" ht="72.04" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="Q6" s="24"/>
     </row>
-    <row r="7" ht="64.69" customHeight="true">
+    <row r="7" ht="72.04" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="64.69" customHeight="true">
+    <row r="8" ht="72.04" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
       </c>
       <c r="Q8" s="23"/>
     </row>
-    <row r="9" ht="64.69" customHeight="true">
+    <row r="9" ht="72.04" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="Q9" s="23"/>
     </row>
-    <row r="10" ht="64.69" customHeight="true">
+    <row r="10" ht="72.04" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -5139,7 +5139,7 @@
       </c>
       <c r="Q10" s="24"/>
     </row>
-    <row r="11" ht="64.69" customHeight="true">
+    <row r="11" ht="72.04" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="64.69" customHeight="true">
+    <row r="12" ht="72.04" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
       </c>
       <c r="Q12" s="23"/>
     </row>
-    <row r="13" ht="64.69" customHeight="true">
+    <row r="13" ht="72.04" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -5323,7 +5323,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="64.69" customHeight="true">
+    <row r="14" ht="72.04" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="64.69" customHeight="true">
+    <row r="15" ht="72.04" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="64.69" customHeight="true">
+    <row r="16" ht="72.04" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
       </c>
       <c r="Q16" s="23"/>
     </row>
-    <row r="17" ht="64.69" customHeight="true">
+    <row r="17" ht="72.04" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -5531,7 +5531,7 @@
       </c>
       <c r="Q17" s="23"/>
     </row>
-    <row r="18" ht="64.69" customHeight="true">
+    <row r="18" ht="72.04" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -5588,6 +5588,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="69"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
 </worksheet>
 </file>